--- a/testdata/MOCK_DATA.xlsx
+++ b/testdata/MOCK_DATA.xlsx
@@ -67,458 +67,359 @@
   <sheetPr>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.2898876404"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.6898876404"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="10.7898876404"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.5898876404"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.6898876404"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.1898876404"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="23.9898876404"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="11.8898876404"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.7898876404"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="27.2898876404"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="1129.4898876404"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="16.2898876404"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.7898876404"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="251.6898876404"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>test_case_name</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>thumbnail_url</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>product_category</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>product_price</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
-          <t>ip_address</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>password</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>username</t>
+          <t>product_description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Larine</t>
+          <t>Magnetic Puzzle Board</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>Rutt</t>
+          <t>https://blogspot.com/molestie/lorem/quisque/ut/erat/curabitur.png?massa=nibh&amp;tempor=in&amp;convallis=hac&amp;nulla=habitasse&amp;neque=platea&amp;libero=dictumst&amp;convallis=aliquam&amp;eget=augue&amp;eleifend=quam&amp;luctus=sollicitudin&amp;ultricies=vitae&amp;eu=consectetuer&amp;nibh=eget&amp;quisque=rutrum&amp;id=at&amp;justo=lorem&amp;sit=integer&amp;amet=tincidunt&amp;sapien=ante&amp;dignissim=vel&amp;vestibulum=ipsum&amp;vestibulum=praesent&amp;ante=blandit&amp;ipsum=lacinia&amp;primis=erat&amp;in=vestibulum&amp;faucibus=sed&amp;orci=magna&amp;luctus=at&amp;et=nunc&amp;ultrices=commodo&amp;posuere=placerat&amp;cubilia=praesent&amp;curae=blandit&amp;nulla=nam&amp;dapibus=nulla&amp;dolor=integer&amp;vel=pede&amp;est=justo&amp;donec=lacinia&amp;odio=eget&amp;justo=tincidunt&amp;sollicitudin=eget&amp;ut=tempus&amp;suscipit=vel&amp;a=pede&amp;feugiat=morbi&amp;et=porttitor&amp;eros=lorem&amp;vestibulum=id&amp;ac=ligula&amp;est=suspendisse&amp;lacinia=ornare&amp;nisi=consequat&amp;venenatis=lectus&amp;tristique=in&amp;fusce=est&amp;congue=risus&amp;diam=auctor&amp;id=sed&amp;ornare=tristique&amp;imperdiet=in&amp;sapien=tempus&amp;urna=sit&amp;pretium=amet&amp;nisl=sem&amp;ut=fusce&amp;volutpat=consequat&amp;sapien=nulla&amp;arcu=nisl&amp;sed=nunc&amp;augue=nisl&amp;aliquam=duis&amp;erat=bibendum&amp;volutpat=felis&amp;in=sed&amp;congue=interdum&amp;etiam=venenatis&amp;justo=turpis&amp;etiam=enim&amp;pretium=blandit&amp;iaculis=mi&amp;justo=in&amp;in=porttitor&amp;hac=pede&amp;habitasse=justo&amp;platea=eu&amp;dictumst=massa&amp;etiam=donec&amp;faucibus=dapibus&amp;cursus=duis&amp;urna=at&amp;ut=velit&amp;tellus=eu&amp;nulla=est&amp;ut=congue&amp;erat=elementum</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>lrutt0@cnet.com</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>57.12</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>193.75.36.67</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>nE7@xigLl)</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>lrutt0</t>
+          <t>Pellentesque at nulla. Suspendisse potenti. Cras in purus eu magna vulputate luctus.
+Cum sociis natoque penatibus et magnis dis parturient montes, nascetur ridiculus mus. Vivamus vestibulum sagittis sapien. Cum sociis natoque penatibus et magnis dis parturient montes, nascetur ridiculus mus.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="n">
-        <v>2</v>
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Outdoor Adventure Kit</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>Escala</t>
+          <t>https://dell.com/imperdiet/nullam/orci/pede.jpg?porttitor=nibh&amp;pede=in&amp;justo=hac&amp;eu=habitasse&amp;massa=platea&amp;donec=dictumst&amp;dapibus=aliquam&amp;duis=augue&amp;at=quam&amp;velit=sollicitudin&amp;eu=vitae&amp;est=consectetuer&amp;congue=eget&amp;elementum=rutrum&amp;in=at&amp;hac=lorem&amp;habitasse=integer&amp;platea=tincidunt&amp;dictumst=ante&amp;morbi=vel&amp;vestibulum=ipsum&amp;velit=praesent&amp;id=blandit&amp;pretium=lacinia&amp;iaculis=erat&amp;diam=vestibulum&amp;erat=sed</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>sescala1@plala.or.jp</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>331.22</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>100.110.186.14</t>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>rH7_?#QMn2oE(=d,</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
-        <is>
-          <t>sescala1</t>
+          <t>Curabitur gravida nisi at nibh. In hac habitasse platea dictumst. Aliquam augue quam, sollicitudin vitae, consectetuer eget, rutrum at, lorem.
+Integer tincidunt ante vel ipsum. Praesent blandit lacinia erat. Vestibulum sed magna at nunc commodo placerat.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>Ms</t>
+        </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Magdaia</t>
+          <t>Pet Training Pads</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>Nano</t>
+          <t>http://alibaba.com/non/mattis/pulvinar/nulla/pede/ullamcorper.html?in=vel&amp;sapien=nisl&amp;iaculis=duis&amp;congue=ac&amp;vivamus=nibh&amp;metus=fusce&amp;arcu=lacus&amp;adipiscing=purus&amp;molestie=aliquet&amp;hendrerit=at&amp;at=feugiat&amp;vulputate=non&amp;vitae=pretium&amp;nisl=quis&amp;aenean=lectus&amp;lectus=suspendisse&amp;pellentesque=potenti&amp;eget=in&amp;nunc=eleifend&amp;donec=quam&amp;quis=a&amp;orci=odio&amp;eget=in&amp;orci=hac&amp;vehicula=habitasse&amp;condimentum=platea&amp;curabitur=dictumst&amp;in=maecenas&amp;libero=ut&amp;ut=massa&amp;massa=quis&amp;volutpat=augue&amp;convallis=luctus&amp;morbi=tincidunt&amp;odio=nulla&amp;odio=mollis&amp;elementum=molestie&amp;eu=lorem&amp;interdum=quisque&amp;eu=ut&amp;tincidunt=erat&amp;in=curabitur&amp;leo=gravida&amp;maecenas=nisi&amp;pulvinar=at&amp;lobortis=nibh&amp;est=in&amp;phasellus=hac</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>mnano2@behance.net</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>551.34</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>8.165.164.51</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>cA5\+Sk&gt;k.3}~+j"</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>mnano2</t>
+          <t>Duis aliquam convallis nunc. Proin at turpis a pede posuere nonummy. Integer non velit.
+Donec diam neque, vestibulum eget, vulputate ut, ultrices vel, augue. Vestibulum ante ipsum primis in faucibus orci luctus et ultrices posuere cubilia Curae; Donec pharetra, magna vestibulum aliquet ultrices, erat tortor sollicitudin mi, sit amet lobortis sapien sapien non mi. Integer ac neque.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>Dr</t>
+        </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Chaim</t>
+          <t>Chicken Parmesan Dinner Kit</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Feron</t>
+          <t>https://paginegialle.it/sit/amet/consectetuer/adipiscing/elit/proin.aspx?aenean=aliquet&amp;fermentum=at&amp;donec=feugiat&amp;ut=non&amp;mauris=pretium&amp;eget=quis&amp;massa=lectus&amp;tempor=suspendisse&amp;convallis=potenti&amp;nulla=in&amp;neque=eleifend&amp;libero=quam&amp;convallis=a&amp;eget=odio&amp;eleifend=in&amp;luctus=hac&amp;ultricies=habitasse&amp;eu=platea&amp;nibh=dictumst&amp;quisque=maecenas&amp;id=ut&amp;justo=massa&amp;sit=quis&amp;amet=augue&amp;sapien=luctus&amp;dignissim=tincidunt&amp;vestibulum=nulla&amp;vestibulum=mollis&amp;ante=molestie&amp;ipsum=lorem&amp;primis=quisque&amp;in=ut&amp;faucibus=erat&amp;orci=curabitur&amp;luctus=gravida&amp;et=nisi&amp;ultrices=at&amp;posuere=nibh&amp;cubilia=in&amp;curae=hac&amp;nulla=habitasse&amp;dapibus=platea&amp;dolor=dictumst&amp;vel=aliquam&amp;est=augue&amp;donec=quam&amp;odio=sollicitudin&amp;justo=vitae&amp;sollicitudin=consectetuer&amp;ut=eget&amp;suscipit=rutrum&amp;a=at&amp;feugiat=lorem&amp;et=integer&amp;eros=tincidunt&amp;vestibulum=ante&amp;ac=vel&amp;est=ipsum&amp;lacinia=praesent&amp;nisi=blandit&amp;venenatis=lacinia&amp;tristique=erat&amp;fusce=vestibulum&amp;congue=sed&amp;diam=magna&amp;id=at&amp;ornare=nunc&amp;imperdiet=commodo&amp;sapien=placerat&amp;urna=praesent&amp;pretium=blandit&amp;nisl=nam&amp;ut=nulla&amp;volutpat=integer&amp;sapien=pede</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>cferon3@youtu.be</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+          <t>Food - Frozen Meals</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>670.28</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>23.100.213.65</t>
-        </is>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>jH8&amp;l5Q*v`dTFY"f</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>cferon3</t>
+          <t>Maecenas ut massa quis augue luctus tincidunt. Nulla mollis molestie lorem. Quisque ut erat.
+Curabitur gravida nisi at nibh. In hac habitasse platea dictumst. Aliquam augue quam, sollicitudin vitae, consectetuer eget, rutrum at, lorem.
+Integer tincidunt ante vel ipsum. Praesent blandit lacinia erat. Vestibulum sed magna at nunc commodo placerat.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Christalle</t>
+          <t>Buffalo Cauliflower Wings</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>Seelbach</t>
+          <t>https://deliciousdays.com/integer/aliquet.js?accumsan=quis&amp;odio=orci&amp;curabitur=eget&amp;convallis=orci&amp;duis=vehicula&amp;consequat=condimentum</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>cseelbach4@pcworld.com</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>Non-binary</t>
-        </is>
+          <t>Food - Frozen Foods</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>121.81</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>52.121.17.226</t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>cG3'|6`gi</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t>cseelbach4</t>
+          <t>Morbi porttitor lorem id ligula. Suspendisse ornare consequat lectus. In est risus, auctor sed, tristique in, tempus sit amet, sem.
+Fusce consequat. Nulla nisl. Nunc nisl.
+Duis bibendum, felis sed interdum venenatis, turpis enim blandit mi, in porttitor pede justo eu massa. Donec dapibus. Duis at velit eu est congue elementum.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n">
-        <v>6</v>
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Dr</t>
+        </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Scented Candle Set</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>Bows</t>
+          <t>http://columbia.edu/nunc/nisl/duis/bibendum/felis.html?lectus=cum&amp;in=sociis&amp;est=natoque&amp;risus=penatibus&amp;auctor=et&amp;sed=magnis&amp;tristique=dis&amp;in=parturient&amp;tempus=montes&amp;sit=nascetur&amp;amet=ridiculus&amp;sem=mus&amp;fusce=vivamus&amp;consequat=vestibulum&amp;nulla=sagittis&amp;nisl=sapien&amp;nunc=cum&amp;nisl=sociis&amp;duis=natoque&amp;bibendum=penatibus&amp;felis=et&amp;sed=magnis&amp;interdum=dis&amp;venenatis=parturient&amp;turpis=montes&amp;enim=nascetur&amp;blandit=ridiculus&amp;mi=mus&amp;in=etiam&amp;porttitor=vel&amp;pede=augue&amp;justo=vestibulum&amp;eu=rutrum&amp;massa=rutrum&amp;donec=neque&amp;dapibus=aenean&amp;duis=auctor&amp;at=gravida&amp;velit=sem&amp;eu=praesent&amp;est=id&amp;congue=massa&amp;elementum=id&amp;in=nisl&amp;hac=venenatis&amp;habitasse=lacinia&amp;platea=aenean&amp;dictumst=sit&amp;morbi=amet&amp;vestibulum=justo&amp;velit=morbi&amp;id=ut&amp;pretium=odio&amp;iaculis=cras&amp;diam=mi&amp;erat=pede&amp;fermentum=malesuada&amp;justo=in&amp;nec=imperdiet&amp;condimentum=et&amp;neque=commodo&amp;sapien=vulputate&amp;placerat=justo&amp;ante=in&amp;nulla=blandit&amp;justo=ultrices&amp;aliquam=enim&amp;quis=lorem&amp;turpis=ipsum&amp;eget=dolor&amp;elit=sit&amp;sodales=amet&amp;scelerisque=consectetuer&amp;mauris=adipiscing&amp;sit=elit&amp;amet=proin&amp;eros=interdum&amp;suspendisse=mauris&amp;accumsan=non&amp;tortor=ligula&amp;quis=pellentesque&amp;turpis=ultrices&amp;sed=phasellus&amp;ante=id&amp;vivamus=sapien&amp;tortor=in</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>cbows5@twitter.com</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>491.34</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>193.86.127.4</t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>wU0}Z4|l</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>cbows5</t>
+          <t>Fusce consequat. Nulla nisl. Nunc nisl.
+Duis bibendum, felis sed interdum venenatis, turpis enim blandit mi, in porttitor pede justo eu massa. Donec dapibus. Duis at velit eu est congue elementum.
+In hac habitasse platea dictumst. Morbi vestibulum, velit id pretium iaculis, diam erat fermentum justo, nec condimentum neque sapien placerat ante. Nulla justo.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Honorable</t>
+        </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Effie</t>
+          <t>Sesame Garlic Noodles</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Legges</t>
+          <t>https://engadget.com/nisl/nunc/nisl/duis/bibendum.jsp?cubilia=aenean&amp;curae=lectus&amp;duis=pellentesque&amp;faucibus=eget&amp;accumsan=nunc&amp;odio=donec&amp;curabitur=quis&amp;convallis=orci&amp;duis=eget&amp;consequat=orci&amp;dui=vehicula&amp;nec=condimentum&amp;nisi=curabitur&amp;volutpat=in&amp;eleifend=libero</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>elegges6@bbb.org</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+          <t>Food - Pasta</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>502.33</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>78.171.55.234</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>lZ5(_Ku3,</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>elegges6</t>
+          <t>Duis aliquam convallis nunc. Proin at turpis a pede posuere nonummy. Integer non velit.
+Donec diam neque, vestibulum eget, vulputate ut, ultrices vel, augue. Vestibulum ante ipsum primis in faucibus orci luctus et ultrices posuere cubilia Curae; Donec pharetra, magna vestibulum aliquet ultrices, erat tortor sollicitudin mi, sit amet lobortis sapien sapien non mi. Integer ac neque.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Cristiano</t>
+          <t>Comfortable Bed Pillow</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>McPartling</t>
+          <t>https://disqus.com/lectus/aliquam/sit/amet/diam/in/magna.jpg?odio=est&amp;condimentum=et&amp;id=tempus&amp;luctus=semper&amp;nec=est&amp;molestie=quam&amp;sed=pharetra&amp;justo=magna&amp;pellentesque=ac&amp;viverra=consequat&amp;pede=metus&amp;ac=sapien&amp;diam=ut&amp;cras=nunc&amp;pellentesque=vestibulum&amp;volutpat=ante&amp;dui=ipsum&amp;maecenas=primis&amp;tristique=in</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>cmcpartling7@twitter.com</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>138.84</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>19.84.55.175</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>rN5*ZXV42If8F2!</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>cmcpartling7</t>
+          <t>Cum sociis natoque penatibus et magnis dis parturient montes, nascetur ridiculus mus. Vivamus vestibulum sagittis sapien. Cum sociis natoque penatibus et magnis dis parturient montes, nascetur ridiculus mus.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Timotheus</t>
+          <t>Sliced Cucumbers</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Barton</t>
+          <t>http://msu.edu/dolor.png?in=vel&amp;quis=accumsan&amp;justo=tellus&amp;maecenas=nisi&amp;rhoncus=eu&amp;aliquam=orci&amp;lacus=mauris&amp;morbi=lacinia&amp;quis=sapien&amp;tortor=quis&amp;id=libero&amp;nulla=nullam&amp;ultrices=sit&amp;aliquet=amet&amp;maecenas=turpis&amp;leo=elementum&amp;odio=ligula&amp;condimentum=vehicula&amp;id=consequat&amp;luctus=morbi&amp;nec=a&amp;molestie=ipsum&amp;sed=integer&amp;justo=a&amp;pellentesque=nibh&amp;viverra=in&amp;pede=quis&amp;ac=justo&amp;diam=maecenas&amp;cras=rhoncus&amp;pellentesque=aliquam&amp;volutpat=lacus&amp;dui=morbi&amp;maecenas=quis&amp;tristique=tortor&amp;est=id&amp;et=nulla&amp;tempus=ultrices&amp;semper=aliquet&amp;est=maecenas&amp;quam=leo&amp;pharetra=odio&amp;magna=condimentum&amp;ac=id&amp;consequat=luctus&amp;metus=nec&amp;sapien=molestie&amp;ut=sed&amp;nunc=justo&amp;vestibulum=pellentesque&amp;ante=viverra&amp;ipsum=pede&amp;primis=ac&amp;in=diam&amp;faucibus=cras&amp;orci=pellentesque&amp;luctus=volutpat&amp;et=dui&amp;ultrices=maecenas&amp;posuere=tristique&amp;cubilia=est&amp;curae=et&amp;mauris=tempus&amp;viverra=semper&amp;diam=est&amp;vitae=quam&amp;quam=pharetra&amp;suspendisse=magna&amp;potenti=ac&amp;nullam=consequat&amp;porttitor=metus&amp;lacus=sapien&amp;at=ut&amp;turpis=nunc&amp;donec=vestibulum&amp;posuere=ante&amp;metus=ipsum&amp;vitae=primis&amp;ipsum=in&amp;aliquam=faucibus&amp;non=orci</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>tbarton8@wufoo.com</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+          <t>Food - Produce</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>415.29</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>1.179.7.38</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>gU6_Ga_Lu</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>tbarton8</t>
+          <t>Lorem ipsum dolor sit amet, consectetuer adipiscing elit. Proin risus. Praesent lectus.
+Vestibulum quam sapien, varius ut, blandit non, interdum in, ante. Vestibulum ante ipsum primis in faucibus orci luctus et ultrices posuere cubilia Curae; Duis faucibus accumsan odio. Curabitur convallis.
+Duis consequat dui nec nisi volutpat eleifend. Donec ut dolor. Morbi vel lectus in quam fringilla rhoncus.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Clerc</t>
+          <t>Children's Musical Instrument Set</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Gouldeby</t>
+          <t>https://hc360.com/maecenas/pulvinar/lobortis/est/phasellus.png?vestibulum=turpis&amp;aliquet=adipiscing&amp;ultrices=lorem&amp;erat=vitae&amp;tortor=mattis&amp;sollicitudin=nibh&amp;mi=ligula&amp;sit=nec&amp;amet=sem&amp;lobortis=duis&amp;sapien=aliquam&amp;sapien=convallis&amp;non=nunc&amp;mi=proin&amp;integer=at&amp;ac=turpis&amp;neque=a&amp;duis=pede&amp;bibendum=posuere&amp;morbi=nonummy&amp;non=integer&amp;quam=non&amp;nec=velit&amp;dui=donec&amp;luctus=diam&amp;rutrum=neque&amp;nulla=vestibulum&amp;tellus=eget&amp;in=vulputate&amp;sagittis=ut&amp;dui=ultrices&amp;vel=vel&amp;nisl=augue&amp;duis=vestibulum&amp;ac=ante&amp;nibh=ipsum&amp;fusce=primis&amp;lacus=in&amp;purus=faucibus&amp;aliquet=orci&amp;at=luctus&amp;feugiat=et&amp;non=ultrices&amp;pretium=posuere&amp;quis=cubilia&amp;lectus=curae&amp;suspendisse=donec&amp;potenti=pharetra&amp;in=magna&amp;eleifend=vestibulum&amp;quam=aliquet&amp;a=ultrices&amp;odio=erat&amp;in=tortor&amp;hac=sollicitudin&amp;habitasse=mi&amp;platea=sit&amp;dictumst=amet&amp;maecenas=lobortis&amp;ut=sapien&amp;massa=sapien&amp;quis=non&amp;augue=mi&amp;luctus=integer&amp;tincidunt=ac&amp;nulla=neque&amp;mollis=duis&amp;molestie=bibendum&amp;lorem=morbi&amp;quisque=non&amp;ut=quam&amp;erat=nec</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>cgouldeby9@youtu.be</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>581.94</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>131.128.54.181</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>zV1,7X'~</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>cgouldeby9</t>
+          <t>Fusce posuere felis sed lacus. Morbi sem mauris, laoreet ut, rhoncus aliquet, pulvinar sed, nisl. Nunc rhoncus dui vel sem.
+Sed sagittis. Nam congue, risus semper porta volutpat, quam pede lobortis ligula, sit amet eleifend pede libero quis orci. Nullam molestie nibh in lectus.</t>
         </is>
       </c>
     </row>
